--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3137,6 +3137,1753 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126596765</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>730730</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7217504</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126596766</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>730582</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7217528</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126596772</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>730566</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7217515</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126596771</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>730552</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7217450</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126596757</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>730596</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7217593</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126596775</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92727</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>730596</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7217593</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126596760</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>730603</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7217653</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126596773</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>730581</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7217533</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126596783</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>730579</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7217528</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126596764</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>730737</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7217503</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126596778</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>730497</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7217488</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126596776</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>730588</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7217644</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126596763</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>730705</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7217522</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126596761</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>730575</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7217530</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126596767</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>730581</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7217533</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126596782</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>730612</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7217449</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126596784</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91506</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>65</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>730766</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7217447</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -3464,32 +3464,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126596757</v>
+        <v>126596775</v>
       </c>
       <c r="B27" t="n">
-        <v>91210</v>
+        <v>92802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126596775</v>
+        <v>126596771</v>
       </c>
       <c r="B28" t="n">
-        <v>92727</v>
+        <v>57817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,34 +3572,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730596</v>
+        <v>730552</v>
       </c>
       <c r="R28" t="n">
-        <v>7217593</v>
+        <v>7217450</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3658,53 +3666,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126596771</v>
+        <v>126596757</v>
       </c>
       <c r="B29" t="n">
-        <v>57817</v>
+        <v>91284</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730552</v>
+        <v>730596</v>
       </c>
       <c r="R29" t="n">
-        <v>7217450</v>
+        <v>7217593</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,7 +3766,7 @@
         <v>126596760</v>
       </c>
       <c r="B30" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>126596783</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126596778</v>
+        <v>126596761</v>
       </c>
       <c r="B34" t="n">
-        <v>56840</v>
+        <v>79629</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,42 +4183,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730497</v>
+        <v>730575</v>
       </c>
       <c r="R34" t="n">
-        <v>7217488</v>
+        <v>7217530</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4280,7 +4272,7 @@
         <v>126596776</v>
       </c>
       <c r="B35" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,10 +4367,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126596761</v>
+        <v>126596763</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4386,34 +4378,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730575</v>
+        <v>730705</v>
       </c>
       <c r="R36" t="n">
-        <v>7217530</v>
+        <v>7217522</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4446,6 +4446,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4472,10 +4477,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126596763</v>
+        <v>126596778</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4483,16 +4488,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4502,12 +4507,12 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4515,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730705</v>
+        <v>730497</v>
       </c>
       <c r="R37" t="n">
-        <v>7217522</v>
+        <v>7217488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4551,11 +4556,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4582,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126596767</v>
+        <v>126596782</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>91337</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,42 +4593,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730581</v>
+        <v>730612</v>
       </c>
       <c r="R38" t="n">
-        <v>7217533</v>
+        <v>7217449</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4661,11 +4653,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4692,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126596782</v>
+        <v>126596767</v>
       </c>
       <c r="B39" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4703,34 +4690,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730612</v>
+        <v>730581</v>
       </c>
       <c r="R39" t="n">
-        <v>7217449</v>
+        <v>7217533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4763,6 +4758,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4792,7 +4792,7 @@
         <v>126596784</v>
       </c>
       <c r="B40" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126596775</v>
+        <v>126596771</v>
       </c>
       <c r="B27" t="n">
-        <v>92802</v>
+        <v>57817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,34 +3475,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730596</v>
+        <v>730552</v>
       </c>
       <c r="R27" t="n">
-        <v>7217593</v>
+        <v>7217450</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126596771</v>
+        <v>126596775</v>
       </c>
       <c r="B28" t="n">
-        <v>57817</v>
+        <v>92808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,42 +3580,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730552</v>
+        <v>730596</v>
       </c>
       <c r="R28" t="n">
-        <v>7217450</v>
+        <v>7217593</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>126596757</v>
       </c>
       <c r="B29" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>126596760</v>
       </c>
       <c r="B30" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>126596783</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>126596761</v>
       </c>
       <c r="B34" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126596776</v>
+        <v>126596763</v>
       </c>
       <c r="B35" t="n">
-        <v>78770</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,34 +4280,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730588</v>
+        <v>730705</v>
       </c>
       <c r="R35" t="n">
-        <v>7217644</v>
+        <v>7217522</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4342,13 +4350,17 @@
           <t>2025-07-11</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4367,10 +4379,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126596763</v>
+        <v>126596778</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4378,16 +4390,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4397,12 +4409,12 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4410,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730705</v>
+        <v>730497</v>
       </c>
       <c r="R36" t="n">
-        <v>7217522</v>
+        <v>7217488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4446,11 +4458,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4477,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126596778</v>
+        <v>126596776</v>
       </c>
       <c r="B37" t="n">
-        <v>56840</v>
+        <v>78773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4488,42 +4495,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730497</v>
+        <v>730588</v>
       </c>
       <c r="R37" t="n">
-        <v>7217488</v>
+        <v>7217644</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4564,6 +4563,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>126596782</v>
       </c>
       <c r="B38" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>126596784</v>
       </c>
       <c r="B40" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126596765</v>
+        <v>126596766</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730730</v>
+        <v>730582</v>
       </c>
       <c r="R24" t="n">
-        <v>7217504</v>
+        <v>7217528</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126596766</v>
+        <v>126596765</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730582</v>
+        <v>730730</v>
       </c>
       <c r="R25" t="n">
-        <v>7217528</v>
+        <v>7217504</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126596771</v>
+        <v>126596775</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>92808</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,42 +3475,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730552</v>
+        <v>730596</v>
       </c>
       <c r="R27" t="n">
-        <v>7217450</v>
+        <v>7217593</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,32 +3561,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126596775</v>
+        <v>126596757</v>
       </c>
       <c r="B28" t="n">
-        <v>92808</v>
+        <v>91290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,45 +3658,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126596757</v>
+        <v>126596771</v>
       </c>
       <c r="B29" t="n">
-        <v>91290</v>
+        <v>57817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Petikån, norr, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730596</v>
+        <v>730552</v>
       </c>
       <c r="R29" t="n">
-        <v>7217593</v>
+        <v>7217450</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126596763</v>
+        <v>126596778</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,16 +4280,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730705</v>
+        <v>730497</v>
       </c>
       <c r="R35" t="n">
-        <v>7217522</v>
+        <v>7217488</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4348,11 +4348,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4379,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126596778</v>
+        <v>126596763</v>
       </c>
       <c r="B36" t="n">
-        <v>56840</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4409,12 +4404,12 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730497</v>
+        <v>730705</v>
       </c>
       <c r="R36" t="n">
-        <v>7217488</v>
+        <v>7217522</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4458,6 +4453,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -4889,7 +4889,7 @@
         <v>127020651</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -4889,7 +4889,7 @@
         <v>127020651</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4994,6 +4994,302 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128105041</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Klövertjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>730601</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7217706</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128105038</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90384</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Klövertjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>730578</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7217535</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128105039</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92643</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Klövertjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>730725</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7217511</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -5101,7 +5101,7 @@
         <v>128105038</v>
       </c>
       <c r="B43" t="n">
-        <v>90384</v>
+        <v>90385</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128105039</v>
       </c>
       <c r="B44" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -4999,7 +4999,7 @@
         <v>128105041</v>
       </c>
       <c r="B42" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128105038</v>
       </c>
       <c r="B43" t="n">
-        <v>90387</v>
+        <v>90393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128105039</v>
       </c>
       <c r="B44" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -4999,7 +4999,7 @@
         <v>128105041</v>
       </c>
       <c r="B42" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128105038</v>
       </c>
       <c r="B43" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128105039</v>
       </c>
       <c r="B44" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -4999,7 +4999,7 @@
         <v>128105041</v>
       </c>
       <c r="B42" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128105038</v>
       </c>
       <c r="B43" t="n">
-        <v>90485</v>
+        <v>90497</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128105039</v>
       </c>
       <c r="B44" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 32238-2024 artfynd.xlsx
+++ b/artfynd/A 32238-2024 artfynd.xlsx
@@ -5101,7 +5101,7 @@
         <v>128105038</v>
       </c>
       <c r="B43" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128105039</v>
       </c>
       <c r="B44" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
